--- a/jogos_2024-12-05.xlsx
+++ b/jogos_2024-12-05.xlsx
@@ -1417,25 +1417,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
         <v>1</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.3</v>
+        <v>4.75</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="N8" t="n">
-        <v>2.88</v>
+        <v>1.7</v>
       </c>
       <c r="O8" t="n">
-        <v>2.61</v>
+        <v>4.5</v>
       </c>
       <c r="P8" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.62</v>
+        <v>2.15</v>
       </c>
       <c r="R8" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="T8" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="U8" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="V8" t="n">
         <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X8" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.57</v>
+        <v>2.85</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['88']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['29']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.34</v>
+        <v>2.2</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.69</v>
+        <v>1.15</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.74</v>
+        <v>2.75</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.17</v>
+        <v>1.53</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45631.5625</v>
@@ -1546,25 +1546,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
         <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.75</v>
+        <v>2.3</v>
       </c>
       <c r="M9" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N9" t="n">
-        <v>1.7</v>
+        <v>2.88</v>
       </c>
       <c r="O9" t="n">
-        <v>4.5</v>
+        <v>2.61</v>
       </c>
       <c r="P9" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.15</v>
+        <v>3.62</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S9" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="T9" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="U9" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="V9" t="n">
         <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.85</v>
+        <v>2.57</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
+          <t>['88']</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>['29']</t>
-        </is>
-      </c>
       <c r="AG9" t="n">
-        <v>2.2</v>
+        <v>1.34</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.15</v>
+        <v>1.69</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.75</v>
+        <v>1.74</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.53</v>
+        <v>2.17</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45631.5625</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Milan II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2077,10 +2077,10 @@
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="M13" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>8</v>
+        <v>4.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.7</v>
+        <v>2.38</v>
       </c>
       <c r="P13" t="n">
-        <v>2.65</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>3.54</v>
+        <v>2.5</v>
       </c>
       <c r="T13" t="n">
-        <v>2.29</v>
+        <v>3.4</v>
       </c>
       <c r="U13" t="n">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W13" t="n">
-        <v>1.14</v>
+        <v>1.42</v>
       </c>
       <c r="X13" t="n">
-        <v>4.55</v>
+        <v>2.75</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.43</v>
+        <v>4.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AD13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>['7']</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>['31']</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AH13" t="n">
         <v>1.76</v>
       </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>['67']</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>['90+4']</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AI13" t="n">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="AJ13" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45631.66666666666</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Milan II</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2335,10 +2335,10 @@
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M15" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="N15" t="n">
+        <v>8</v>
+      </c>
+      <c r="O15" t="n">
         <v>1.7</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.38</v>
-      </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>2.65</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5</v>
+        <v>3.54</v>
       </c>
       <c r="T15" t="n">
-        <v>3.4</v>
+        <v>2.29</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W15" t="n">
-        <v>1.42</v>
+        <v>1.14</v>
       </c>
       <c r="X15" t="n">
-        <v>2.75</v>
+        <v>4.55</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.2</v>
+        <v>2.43</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['7']</t>
+          <t>['67']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['31']</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.76</v>
+        <v>3.6</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AJ15" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45631.66666666666</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,109 +2578,109 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" t="n">
         <v>1</v>
       </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
       <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.15</v>
+        <v>8</v>
       </c>
       <c r="M17" t="n">
-        <v>3.56</v>
+        <v>5</v>
       </c>
       <c r="N17" t="n">
-        <v>2.2</v>
+        <v>1.36</v>
       </c>
       <c r="O17" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>['19', '35']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>['12']</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
         <v>3</v>
       </c>
-      <c r="P17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S17" t="n">
-        <v>4</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>['17']</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.51</v>
+        <v>1.07</v>
       </c>
       <c r="AI17" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45631.71875</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,109 +2707,109 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>['17']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AI18" t="n">
         <v>2</v>
       </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>8</v>
-      </c>
-      <c r="M18" t="n">
-        <v>5</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="O18" t="n">
-        <v>8.34</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>['19', '35']</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>['12']</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AJ18" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45631.71875</v>
@@ -2836,25 +2836,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R19" t="n">
         <v>1.4</v>
       </c>
-      <c r="M19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N19" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>9</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.44</v>
-      </c>
       <c r="S19" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="T19" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U19" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V19" t="n">
         <v>1.06</v>
       </c>
       <c r="W19" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="X19" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Z19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>['74']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>['15', '82']</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI19" t="n">
         <v>1.62</v>
       </c>
-      <c r="AA19" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>['59']</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AJ19" t="n">
-        <v>4.75</v>
+        <v>2.5</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45631.83333333334</v>
@@ -2965,25 +2965,25 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.05</v>
+        <v>1.4</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="N20" t="n">
-        <v>3.8</v>
+        <v>8.5</v>
       </c>
       <c r="O20" t="n">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.33</v>
+        <v>9</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T20" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U20" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
         <v>1.06</v>
       </c>
       <c r="W20" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="X20" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.8</v>
+        <v>2.63</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['74']</t>
+          <t>['59']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['15', '82']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.5</v>
+        <v>4.75</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45631.83333333334</v>
